--- a/out/daily_positions.xlsx
+++ b/out/daily_positions.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3D3D3"/>
+        <bgColor rgb="00D3D3D3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +428,989 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>gross_amount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>avg_trade_price</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>R$ 11.641,55</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>R$ 14,83</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>R$ 99,05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>R$ 186.798,40</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>R$ 52,44</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>R$ 109,05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>BOVA11</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>R$ 15.272,50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>R$ 122,18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>R$ 167,04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>R$ 19.793,52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>R$ 29,72</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>R$ 136,08</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>R$ 80.748,75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,30</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>R$ 194,94</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>R$ 17.602,50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,03</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>R$ 158,74</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>R$ 28.837,80</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,97</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>R$ 162,25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21.274,88</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>R$ 15,11</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>R$ 200,91</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>R$ 114.952,27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>R$ 52,67</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>R$ 137,31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>BOVA11</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>R$ 410.228,62</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>R$ 123,88</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>R$ 183,32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>R$ 112.174,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>R$ 29,87</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>R$ 260,02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>R$ 120.833,71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,45</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>R$ 240,94</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>R$ 243.057,15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,95</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>R$ 207,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>R$ 29.672,92</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,14</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,76</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>R$ 7.352,60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>R$ 15,16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,94</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166.688,81</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,50</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>R$ 162,68</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BOVA11</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.105,28</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>R$ 123,84</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>R$ 129,90</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>R$ 3.923,96</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>R$ 29,84</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>R$ 131,84</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>R$ 87.161,37</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,32</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>R$ 208,59</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>R$ 17.884,74</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,92</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>R$ 127,31</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42.043,75</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,75</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>R$ 138,18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>R$ 28.930,54</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>R$ 14,80</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>R$ 177,43</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 186.997,36</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 52,06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 136,42</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>BOVA11</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>R$ 357.124,83</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>R$ 122,74</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,73</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>R$ 28.863,87</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>R$ 30,13</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>R$ 206,04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>R$ 17.768,04</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,39</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>R$ 222,45</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33.352,54</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,34</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>R$ 109,34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38.120,58</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,84</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>R$ 252,92</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ABEV3</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>R$ 18.330,00</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>R$ 15,00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>R$ 110,66</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>BBAS3</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>R$ 344.452,42</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,43</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>R$ 252,26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>BOVA11</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>R$ 154.292,43</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>R$ 120,73</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>R$ 232,42</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ITUB4</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>R$ 50.756,53</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>R$ 29,39</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,99</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>R$ 4.009,79</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,02</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>R$ 169,34</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>R$ 109.216,80</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,95</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>R$ 152,67</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>WEGE3</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>R$ 20.955,25</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>R$ 153,62</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>